--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N82_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N82_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.12369219600422</v>
+        <v>5.707599981850686</v>
       </c>
       <c r="D2" t="n">
-        <v>35.87651022560399</v>
+        <v>5.829932911660648</v>
       </c>
       <c r="E2" t="n">
-        <v>12.22094271957596</v>
+        <v>1.985903191931093</v>
       </c>
       <c r="F2" t="n">
-        <v>12.80858762690002</v>
+        <v>2.081395489371253</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>35.5667771293801</v>
+        <v>5.779601283524267</v>
       </c>
       <c r="D3" t="n">
-        <v>36.03466736958407</v>
+        <v>5.855633447557412</v>
       </c>
       <c r="E3" t="n">
-        <v>12.22094271957596</v>
+        <v>1.985903191931093</v>
       </c>
       <c r="F3" t="n">
-        <v>12.80858762690002</v>
+        <v>2.081395489371253</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>21.13317792679481</v>
+        <v>3.434141413104157</v>
       </c>
       <c r="D4" t="n">
-        <v>21.68880432871136</v>
+        <v>3.524430703415597</v>
       </c>
       <c r="E4" t="n">
-        <v>12.22094271957596</v>
+        <v>1.985903191931093</v>
       </c>
       <c r="F4" t="n">
-        <v>12.80858762690002</v>
+        <v>2.081395489371253</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>31.57985266783529</v>
+        <v>5.131726058523235</v>
       </c>
       <c r="D5" t="n">
-        <v>31.43761057459318</v>
+        <v>5.108611718371392</v>
       </c>
       <c r="E5" t="n">
-        <v>12.22094271957596</v>
+        <v>1.985903191931093</v>
       </c>
       <c r="F5" t="n">
-        <v>12.80858762690002</v>
+        <v>2.081395489371253</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>30.72761907510143</v>
+        <v>4.993238099703983</v>
       </c>
       <c r="D6" t="n">
-        <v>30.33211537280476</v>
+        <v>4.928968748080774</v>
       </c>
       <c r="E6" t="n">
-        <v>12.22094271957596</v>
+        <v>1.985903191931093</v>
       </c>
       <c r="F6" t="n">
-        <v>12.80858762690002</v>
+        <v>2.081395489371253</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>50.39672374611282</v>
+        <v>8.189467608743334</v>
       </c>
       <c r="D7" t="n">
-        <v>52.18960770685176</v>
+        <v>8.480811252363411</v>
       </c>
       <c r="E7" t="n">
-        <v>12.22094271957596</v>
+        <v>1.985903191931093</v>
       </c>
       <c r="F7" t="n">
-        <v>12.80858762690002</v>
+        <v>2.081395489371253</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>52.30456507664755</v>
+        <v>8.499491824955227</v>
       </c>
       <c r="D8" t="n">
-        <v>54.11580896609586</v>
+        <v>8.793818956990577</v>
       </c>
       <c r="E8" t="n">
-        <v>12.22094271957596</v>
+        <v>1.985903191931093</v>
       </c>
       <c r="F8" t="n">
-        <v>12.80858762690002</v>
+        <v>2.081395489371253</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>28.70713437466724</v>
+        <v>4.664909335883427</v>
       </c>
       <c r="D9" t="n">
-        <v>28.04038032661651</v>
+        <v>4.556561803075184</v>
       </c>
       <c r="E9" t="n">
-        <v>12.22094271957596</v>
+        <v>1.985903191931093</v>
       </c>
       <c r="F9" t="n">
-        <v>12.80858762690002</v>
+        <v>2.081395489371253</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>41.45308507023757</v>
+        <v>6.736126323913606</v>
       </c>
       <c r="D10" t="n">
-        <v>43.15428233325717</v>
+        <v>7.012570879154291</v>
       </c>
       <c r="E10" t="n">
-        <v>12.22094271957596</v>
+        <v>1.985903191931093</v>
       </c>
       <c r="F10" t="n">
-        <v>12.80858762690002</v>
+        <v>2.081395489371253</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>43.33560857493524</v>
+        <v>7.042036393426978</v>
       </c>
       <c r="D11" t="n">
-        <v>45.0660796812282</v>
+        <v>7.323237948199582</v>
       </c>
       <c r="E11" t="n">
-        <v>12.22094271957596</v>
+        <v>1.985903191931093</v>
       </c>
       <c r="F11" t="n">
-        <v>12.80858762690002</v>
+        <v>2.081395489371253</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>35.10404435853755</v>
+        <v>5.704407208262352</v>
       </c>
       <c r="D12" t="n">
-        <v>34.39549637955978</v>
+        <v>5.589268161678465</v>
       </c>
       <c r="E12" t="n">
-        <v>12.22094271957596</v>
+        <v>1.985903191931093</v>
       </c>
       <c r="F12" t="n">
-        <v>12.80858762690002</v>
+        <v>2.081395489371253</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>32.27519480916177</v>
+        <v>5.244719156488789</v>
       </c>
       <c r="D13" t="n">
-        <v>31.48267703767527</v>
+        <v>5.115935018622231</v>
       </c>
       <c r="E13" t="n">
-        <v>12.22094271957596</v>
+        <v>1.985903191931093</v>
       </c>
       <c r="F13" t="n">
-        <v>12.80858762690002</v>
+        <v>2.081395489371253</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>38.04670924600127</v>
+        <v>6.182590252475206</v>
       </c>
       <c r="D14" t="n">
-        <v>36.9761950069104</v>
+        <v>6.00863168862294</v>
       </c>
       <c r="E14" t="n">
-        <v>12.22094271957596</v>
+        <v>1.985903191931093</v>
       </c>
       <c r="F14" t="n">
-        <v>12.80858762690002</v>
+        <v>2.081395489371253</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>25.70734211447091</v>
+        <v>4.177443093601522</v>
       </c>
       <c r="D15" t="n">
-        <v>25.72020659514991</v>
+        <v>4.17953357171186</v>
       </c>
       <c r="E15" t="n">
-        <v>12.22094271957596</v>
+        <v>1.985903191931093</v>
       </c>
       <c r="F15" t="n">
-        <v>12.80858762690002</v>
+        <v>2.081395489371253</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>2.89893497679018</v>
+        <v>0.4710769337284042</v>
       </c>
       <c r="D16" t="n">
-        <v>1.426771164273904</v>
+        <v>0.2318503141945094</v>
       </c>
       <c r="E16" t="n">
-        <v>12.22094271957596</v>
+        <v>1.985903191931093</v>
       </c>
       <c r="F16" t="n">
-        <v>12.80858762690002</v>
+        <v>2.081395489371253</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>22.3591677690936</v>
+        <v>3.633364762477709</v>
       </c>
       <c r="D17" t="n">
-        <v>21.59202761893108</v>
+        <v>3.508704488076301</v>
       </c>
       <c r="E17" t="n">
-        <v>12.22094271957596</v>
+        <v>1.985903191931093</v>
       </c>
       <c r="F17" t="n">
-        <v>12.80858762690002</v>
+        <v>2.081395489371253</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>42.57035693559642</v>
+        <v>6.917683002034419</v>
       </c>
       <c r="D18" t="n">
-        <v>41.61110123357884</v>
+        <v>6.761803950456562</v>
       </c>
       <c r="E18" t="n">
-        <v>12.22094271957596</v>
+        <v>1.985903191931093</v>
       </c>
       <c r="F18" t="n">
-        <v>12.80858762690002</v>
+        <v>2.081395489371253</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>16.66314512042957</v>
+        <v>2.707761082069806</v>
       </c>
       <c r="D19" t="n">
-        <v>16.34114926524487</v>
+        <v>2.655436755602291</v>
       </c>
       <c r="E19" t="n">
-        <v>12.22094271957596</v>
+        <v>1.985903191931093</v>
       </c>
       <c r="F19" t="n">
-        <v>12.80858762690002</v>
+        <v>2.081395489371253</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>15.80766322081097</v>
+        <v>2.568745273381783</v>
       </c>
       <c r="D20" t="n">
-        <v>14.89290852309896</v>
+        <v>2.420097635003581</v>
       </c>
       <c r="E20" t="n">
-        <v>12.22094271957596</v>
+        <v>1.985903191931093</v>
       </c>
       <c r="F20" t="n">
-        <v>12.80858762690002</v>
+        <v>2.081395489371253</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>47.71920712559452</v>
+        <v>7.75437115790911</v>
       </c>
       <c r="D21" t="n">
-        <v>48.06289916771769</v>
+        <v>7.810221114754125</v>
       </c>
       <c r="E21" t="n">
-        <v>12.22094271957596</v>
+        <v>1.985903191931093</v>
       </c>
       <c r="F21" t="n">
-        <v>12.80858762690002</v>
+        <v>2.081395489371253</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>39.84740643697022</v>
+        <v>6.475203546007661</v>
       </c>
       <c r="D22" t="n">
-        <v>39.587900726609</v>
+        <v>6.433033868073963</v>
       </c>
       <c r="E22" t="n">
-        <v>12.22094271957596</v>
+        <v>1.985903191931093</v>
       </c>
       <c r="F22" t="n">
-        <v>12.80858762690002</v>
+        <v>2.081395489371253</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>17.14319672708775</v>
+        <v>2.78576946815176</v>
       </c>
       <c r="D23" t="n">
-        <v>17.76528117638023</v>
+        <v>2.886858191161787</v>
       </c>
       <c r="E23" t="n">
-        <v>12.22094271957596</v>
+        <v>1.985903191931093</v>
       </c>
       <c r="F23" t="n">
-        <v>12.80858762690002</v>
+        <v>2.081395489371253</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
